--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/04_卓越运营与性能效率巡检问题清单.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/04_卓越运营与性能效率巡检问题清单.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azs1\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-kk_29knp\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A52F0F47-9458-4D99-9DD4-21675C7C1533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD58CF00-80E7-4E0D-B856-5F8B0C0D8ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-3645" yWindow="-13320" windowWidth="5970" windowHeight="10455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概览" sheetId="1" r:id="rId1"/>
@@ -1032,7 +1032,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E40A-4B85-A58D-1E622FB0FB0A}"/>
+              <c16:uniqueId val="{00000000-8F45-4158-9CFD-D2D838AA259C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1148,7 +1148,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-E40A-4B85-A58D-1E622FB0FB0A}"/>
+              <c16:uniqueId val="{00000001-8F45-4158-9CFD-D2D838AA259C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1264,7 +1264,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-E40A-4B85-A58D-1E622FB0FB0A}"/>
+              <c16:uniqueId val="{00000002-8F45-4158-9CFD-D2D838AA259C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1458,7 +1458,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E660-4E7B-89BC-7578ED5A74E3}"/>
+              <c16:uniqueId val="{00000000-1C8B-4746-A341-CA53335E554C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1574,7 +1574,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-E660-4E7B-89BC-7578ED5A74E3}"/>
+              <c16:uniqueId val="{00000001-1C8B-4746-A341-CA53335E554C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1690,7 +1690,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-E660-4E7B-89BC-7578ED5A74E3}"/>
+              <c16:uniqueId val="{00000002-1C8B-4746-A341-CA53335E554C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>51</v>
       </c>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/04_卓越运营与性能效率巡检问题清单.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/04_卓越运营与性能效率巡检问题清单.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-kk_29knp\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-lhcbnfs4\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD58CF00-80E7-4E0D-B856-5F8B0C0D8ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{703DA43E-4695-4EBB-8672-1538BB325681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3645" yWindow="-13320" windowWidth="5970" windowHeight="10455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17190" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概览" sheetId="1" r:id="rId1"/>
@@ -1032,7 +1032,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8F45-4158-9CFD-D2D838AA259C}"/>
+              <c16:uniqueId val="{00000000-A312-4A33-9CC4-06063660DD32}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1148,7 +1148,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-8F45-4158-9CFD-D2D838AA259C}"/>
+              <c16:uniqueId val="{00000001-A312-4A33-9CC4-06063660DD32}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1264,7 +1264,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-8F45-4158-9CFD-D2D838AA259C}"/>
+              <c16:uniqueId val="{00000002-A312-4A33-9CC4-06063660DD32}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1458,7 +1458,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1C8B-4746-A341-CA53335E554C}"/>
+              <c16:uniqueId val="{00000000-2553-4CAA-9F9E-E949EF4888E8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1574,7 +1574,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-1C8B-4746-A341-CA53335E554C}"/>
+              <c16:uniqueId val="{00000001-2553-4CAA-9F9E-E949EF4888E8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1690,7 +1690,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-1C8B-4746-A341-CA53335E554C}"/>
+              <c16:uniqueId val="{00000002-2553-4CAA-9F9E-E949EF4888E8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/04_卓越运营与性能效率巡检问题清单.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/04_卓越运营与性能效率巡检问题清单.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-lhcbnfs4\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-yb_0tvu1\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{703DA43E-4695-4EBB-8672-1538BB325681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E627760B-DC3C-4026-AC66-F1583AE90586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17190" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1032,7 +1032,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A312-4A33-9CC4-06063660DD32}"/>
+              <c16:uniqueId val="{00000000-681D-4039-844C-160C2CC95D4B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1148,7 +1148,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-A312-4A33-9CC4-06063660DD32}"/>
+              <c16:uniqueId val="{00000001-681D-4039-844C-160C2CC95D4B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1264,7 +1264,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-A312-4A33-9CC4-06063660DD32}"/>
+              <c16:uniqueId val="{00000002-681D-4039-844C-160C2CC95D4B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1458,7 +1458,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2553-4CAA-9F9E-E949EF4888E8}"/>
+              <c16:uniqueId val="{00000000-4B8F-447C-A7B5-6429083E4865}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1574,7 +1574,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-2553-4CAA-9F9E-E949EF4888E8}"/>
+              <c16:uniqueId val="{00000001-4B8F-447C-A7B5-6429083E4865}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1690,7 +1690,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-2553-4CAA-9F9E-E949EF4888E8}"/>
+              <c16:uniqueId val="{00000002-4B8F-447C-A7B5-6429083E4865}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/04_卓越运营与性能效率巡检问题清单.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/04_卓越运营与性能效率巡检问题清单.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-yb_0tvu1\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-09jfy2fk\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E627760B-DC3C-4026-AC66-F1583AE90586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{012FED84-A240-465E-A794-C3AA77F39388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17190" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2660" yWindow="2660" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概览" sheetId="1" r:id="rId1"/>
@@ -1032,7 +1032,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-681D-4039-844C-160C2CC95D4B}"/>
+              <c16:uniqueId val="{00000000-90A3-4FE6-97DD-E5DEDFE862E6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1148,7 +1148,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-681D-4039-844C-160C2CC95D4B}"/>
+              <c16:uniqueId val="{00000001-90A3-4FE6-97DD-E5DEDFE862E6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1264,7 +1264,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-681D-4039-844C-160C2CC95D4B}"/>
+              <c16:uniqueId val="{00000002-90A3-4FE6-97DD-E5DEDFE862E6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1458,7 +1458,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4B8F-447C-A7B5-6429083E4865}"/>
+              <c16:uniqueId val="{00000000-6A29-400D-A873-20B5E91BC734}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1574,7 +1574,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-4B8F-447C-A7B5-6429083E4865}"/>
+              <c16:uniqueId val="{00000001-6A29-400D-A873-20B5E91BC734}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1690,7 +1690,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-4B8F-447C-A7B5-6429083E4865}"/>
+              <c16:uniqueId val="{00000002-6A29-400D-A873-20B5E91BC734}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>51</v>
       </c>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/04_卓越运营与性能效率巡检问题清单.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/04_卓越运营与性能效率巡检问题清单.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-09jfy2fk\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-5yxkm8zf\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{012FED84-A240-465E-A794-C3AA77F39388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F5D82E-28C2-4DF1-8781-FB771EB6740E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="2660" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概览" sheetId="1" r:id="rId1"/>
@@ -1032,7 +1032,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-90A3-4FE6-97DD-E5DEDFE862E6}"/>
+              <c16:uniqueId val="{00000000-1C3F-4D8F-940D-8801C2010F7E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1148,7 +1148,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-90A3-4FE6-97DD-E5DEDFE862E6}"/>
+              <c16:uniqueId val="{00000001-1C3F-4D8F-940D-8801C2010F7E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1264,7 +1264,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-90A3-4FE6-97DD-E5DEDFE862E6}"/>
+              <c16:uniqueId val="{00000002-1C3F-4D8F-940D-8801C2010F7E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1458,7 +1458,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6A29-400D-A873-20B5E91BC734}"/>
+              <c16:uniqueId val="{00000000-521C-4B40-BE47-4132EAA92A62}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1574,7 +1574,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-6A29-400D-A873-20B5E91BC734}"/>
+              <c16:uniqueId val="{00000001-521C-4B40-BE47-4132EAA92A62}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1690,7 +1690,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-6A29-400D-A873-20B5E91BC734}"/>
+              <c16:uniqueId val="{00000002-521C-4B40-BE47-4132EAA92A62}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/04_卓越运营与性能效率巡检问题清单.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/04_卓越运营与性能效率巡检问题清单.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-5yxkm8zf\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-do642wo4\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F5D82E-28C2-4DF1-8781-FB771EB6740E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36FC74F6-25B3-4176-82D0-916BD6C1BC19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概览" sheetId="1" r:id="rId1"/>
@@ -1032,7 +1032,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1C3F-4D8F-940D-8801C2010F7E}"/>
+              <c16:uniqueId val="{00000000-EBA2-4C0D-A2DD-29AE15289303}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1148,7 +1148,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-1C3F-4D8F-940D-8801C2010F7E}"/>
+              <c16:uniqueId val="{00000001-EBA2-4C0D-A2DD-29AE15289303}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1264,7 +1264,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-1C3F-4D8F-940D-8801C2010F7E}"/>
+              <c16:uniqueId val="{00000002-EBA2-4C0D-A2DD-29AE15289303}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1458,7 +1458,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-521C-4B40-BE47-4132EAA92A62}"/>
+              <c16:uniqueId val="{00000000-95BB-41F3-9B94-B5195BEFD63E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1574,7 +1574,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-521C-4B40-BE47-4132EAA92A62}"/>
+              <c16:uniqueId val="{00000001-95BB-41F3-9B94-B5195BEFD63E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1690,7 +1690,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-521C-4B40-BE47-4132EAA92A62}"/>
+              <c16:uniqueId val="{00000002-95BB-41F3-9B94-B5195BEFD63E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/04_卓越运营与性能效率巡检问题清单.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/04_卓越运营与性能效率巡检问题清单.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-do642wo4\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-jluf97rf\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36FC74F6-25B3-4176-82D0-916BD6C1BC19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1257064C-51A2-48EA-AE9E-FED6FC1A44F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1032,7 +1032,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-EBA2-4C0D-A2DD-29AE15289303}"/>
+              <c16:uniqueId val="{00000000-14BC-4858-B651-3E580F96A2EB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1148,7 +1148,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-EBA2-4C0D-A2DD-29AE15289303}"/>
+              <c16:uniqueId val="{00000001-14BC-4858-B651-3E580F96A2EB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1264,7 +1264,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-EBA2-4C0D-A2DD-29AE15289303}"/>
+              <c16:uniqueId val="{00000002-14BC-4858-B651-3E580F96A2EB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1458,7 +1458,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-95BB-41F3-9B94-B5195BEFD63E}"/>
+              <c16:uniqueId val="{00000000-13DC-4827-BF0C-C3B3CDDD2C93}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1574,7 +1574,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-95BB-41F3-9B94-B5195BEFD63E}"/>
+              <c16:uniqueId val="{00000001-13DC-4827-BF0C-C3B3CDDD2C93}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1690,7 +1690,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-95BB-41F3-9B94-B5195BEFD63E}"/>
+              <c16:uniqueId val="{00000002-13DC-4827-BF0C-C3B3CDDD2C93}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/04_卓越运营与性能效率巡检问题清单.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/04_卓越运营与性能效率巡检问题清单.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-jluf97rf\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-4z_oecii\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1257064C-51A2-48EA-AE9E-FED6FC1A44F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ED8C452-61CD-4D94-85AC-E2B47D7937D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概览" sheetId="1" r:id="rId1"/>
@@ -1032,7 +1032,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-14BC-4858-B651-3E580F96A2EB}"/>
+              <c16:uniqueId val="{00000000-71DB-4C1E-A54B-505514ECC025}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1148,7 +1148,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-14BC-4858-B651-3E580F96A2EB}"/>
+              <c16:uniqueId val="{00000001-71DB-4C1E-A54B-505514ECC025}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1264,7 +1264,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-14BC-4858-B651-3E580F96A2EB}"/>
+              <c16:uniqueId val="{00000002-71DB-4C1E-A54B-505514ECC025}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1458,7 +1458,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-13DC-4827-BF0C-C3B3CDDD2C93}"/>
+              <c16:uniqueId val="{00000000-525B-459C-8A20-7B37B4317C28}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1574,7 +1574,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-13DC-4827-BF0C-C3B3CDDD2C93}"/>
+              <c16:uniqueId val="{00000001-525B-459C-8A20-7B37B4317C28}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1690,7 +1690,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-13DC-4827-BF0C-C3B3CDDD2C93}"/>
+              <c16:uniqueId val="{00000002-525B-459C-8A20-7B37B4317C28}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/04_卓越运营与性能效率巡检问题清单.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/04_卓越运营与性能效率巡检问题清单.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-4z_oecii\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-gq0eyj71\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ED8C452-61CD-4D94-85AC-E2B47D7937D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE74BB6-2007-49E5-B9D6-EF10DEB147F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2280" yWindow="2280" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1032,7 +1032,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-71DB-4C1E-A54B-505514ECC025}"/>
+              <c16:uniqueId val="{00000000-5D16-4C0F-BF71-0043A8FB5FD3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1148,7 +1148,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-71DB-4C1E-A54B-505514ECC025}"/>
+              <c16:uniqueId val="{00000001-5D16-4C0F-BF71-0043A8FB5FD3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1264,7 +1264,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-71DB-4C1E-A54B-505514ECC025}"/>
+              <c16:uniqueId val="{00000002-5D16-4C0F-BF71-0043A8FB5FD3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1458,7 +1458,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-525B-459C-8A20-7B37B4317C28}"/>
+              <c16:uniqueId val="{00000000-1121-4D83-B2E1-3C1F8E58C1B0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1574,7 +1574,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-525B-459C-8A20-7B37B4317C28}"/>
+              <c16:uniqueId val="{00000001-1121-4D83-B2E1-3C1F8E58C1B0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1690,7 +1690,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-525B-459C-8A20-7B37B4317C28}"/>
+              <c16:uniqueId val="{00000002-1121-4D83-B2E1-3C1F8E58C1B0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/04_卓越运营与性能效率巡检问题清单.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/04_卓越运营与性能效率巡检问题清单.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-gq0eyj71\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-9n18lti6\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE74BB6-2007-49E5-B9D6-EF10DEB147F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6116E44-1C58-426A-AE01-323A1C51E8DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2280" yWindow="2280" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1032,7 +1032,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5D16-4C0F-BF71-0043A8FB5FD3}"/>
+              <c16:uniqueId val="{00000000-3B77-4ABD-9C2C-2D1FECD7F058}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1148,7 +1148,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-5D16-4C0F-BF71-0043A8FB5FD3}"/>
+              <c16:uniqueId val="{00000001-3B77-4ABD-9C2C-2D1FECD7F058}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1264,7 +1264,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-5D16-4C0F-BF71-0043A8FB5FD3}"/>
+              <c16:uniqueId val="{00000002-3B77-4ABD-9C2C-2D1FECD7F058}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1458,7 +1458,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1121-4D83-B2E1-3C1F8E58C1B0}"/>
+              <c16:uniqueId val="{00000000-59CF-4B1F-891D-9762F168B815}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1574,7 +1574,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-1121-4D83-B2E1-3C1F8E58C1B0}"/>
+              <c16:uniqueId val="{00000001-59CF-4B1F-891D-9762F168B815}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1690,7 +1690,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-1121-4D83-B2E1-3C1F8E58C1B0}"/>
+              <c16:uniqueId val="{00000002-59CF-4B1F-891D-9762F168B815}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/04_卓越运营与性能效率巡检问题清单.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/04_卓越运营与性能效率巡检问题清单.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30625"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-9n18lti6\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-f6nzzhop\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6116E44-1C58-426A-AE01-323A1C51E8DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD0D372-FBD6-49FD-9BE9-7DABB8D7C285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概览" sheetId="1" r:id="rId1"/>
@@ -1032,7 +1032,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3B77-4ABD-9C2C-2D1FECD7F058}"/>
+              <c16:uniqueId val="{00000000-16EE-4B17-AFA6-091F67A4AEDF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1148,7 +1148,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3B77-4ABD-9C2C-2D1FECD7F058}"/>
+              <c16:uniqueId val="{00000001-16EE-4B17-AFA6-091F67A4AEDF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1264,7 +1264,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-3B77-4ABD-9C2C-2D1FECD7F058}"/>
+              <c16:uniqueId val="{00000002-16EE-4B17-AFA6-091F67A4AEDF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1458,7 +1458,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-59CF-4B1F-891D-9762F168B815}"/>
+              <c16:uniqueId val="{00000000-31A9-4DCD-93F1-F64493E7AF89}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1574,7 +1574,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-59CF-4B1F-891D-9762F168B815}"/>
+              <c16:uniqueId val="{00000001-31A9-4DCD-93F1-F64493E7AF89}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1690,7 +1690,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-59CF-4B1F-891D-9762F168B815}"/>
+              <c16:uniqueId val="{00000002-31A9-4DCD-93F1-F64493E7AF89}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
